--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199346</v>
       </c>
       <c r="B2" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>137199349</v>
       </c>
       <c r="B3" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137209347</v>
       </c>
       <c r="B4" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137209391</v>
       </c>
       <c r="B5" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>137237701</v>
       </c>
       <c r="B6" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137237728</v>
       </c>
       <c r="B7" t="n">
-        <v>79167</v>
+        <v>79169</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137199339</v>
       </c>
       <c r="B8" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137199388</v>
       </c>
       <c r="B9" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137199417</v>
       </c>
       <c r="B10" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137203503</v>
       </c>
       <c r="B11" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>137237700</v>
       </c>
       <c r="B12" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>137237702</v>
       </c>
       <c r="B13" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>137237725</v>
       </c>
       <c r="B14" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137238609</v>
       </c>
       <c r="B15" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137238619</v>
       </c>
       <c r="B16" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137238623</v>
       </c>
       <c r="B17" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>137238624</v>
       </c>
       <c r="B18" t="n">
-        <v>93441</v>
+        <v>93442</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137199403</v>
       </c>
       <c r="B19" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137199406</v>
       </c>
       <c r="B20" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137199408</v>
       </c>
       <c r="B21" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137237704</v>
       </c>
       <c r="B22" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>137237705</v>
       </c>
       <c r="B23" t="n">
-        <v>92164</v>
+        <v>92166</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137199347</v>
       </c>
       <c r="B24" t="n">
-        <v>93467</v>
+        <v>93468</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>137199336</v>
       </c>
       <c r="B96" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>137199341</v>
       </c>
       <c r="B97" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>137199342</v>
       </c>
       <c r="B98" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>137199343</v>
       </c>
       <c r="B99" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>137199351</v>
       </c>
       <c r="B100" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>137199354</v>
       </c>
       <c r="B101" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>137199359</v>
       </c>
       <c r="B102" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>137199360</v>
       </c>
       <c r="B103" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>137199364</v>
       </c>
       <c r="B104" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>137199365</v>
       </c>
       <c r="B105" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>137199378</v>
       </c>
       <c r="B106" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>137199382</v>
       </c>
       <c r="B107" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>137199386</v>
       </c>
       <c r="B108" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>137199387</v>
       </c>
       <c r="B109" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>137199389</v>
       </c>
       <c r="B110" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>137199390</v>
       </c>
       <c r="B111" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>137199395</v>
       </c>
       <c r="B112" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>137199401</v>
       </c>
       <c r="B113" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>137199407</v>
       </c>
       <c r="B114" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>137199416</v>
       </c>
       <c r="B115" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>137199420</v>
       </c>
       <c r="B116" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>137203487</v>
       </c>
       <c r="B117" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>137203488</v>
       </c>
       <c r="B118" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>137203490</v>
       </c>
       <c r="B119" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>137203491</v>
       </c>
       <c r="B120" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>137203493</v>
       </c>
       <c r="B121" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>137203494</v>
       </c>
       <c r="B122" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>137203496</v>
       </c>
       <c r="B123" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>137203502</v>
       </c>
       <c r="B124" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>137203504</v>
       </c>
       <c r="B125" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>137203505</v>
       </c>
       <c r="B126" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>137203506</v>
       </c>
       <c r="B127" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>137203507</v>
       </c>
       <c r="B128" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>137203508</v>
       </c>
       <c r="B129" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>137203509</v>
       </c>
       <c r="B130" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>137203510</v>
       </c>
       <c r="B131" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>137203511</v>
       </c>
       <c r="B132" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>137203512</v>
       </c>
       <c r="B133" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>137203513</v>
       </c>
       <c r="B134" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>137203514</v>
       </c>
       <c r="B135" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>137203515</v>
       </c>
       <c r="B136" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>137209346</v>
       </c>
       <c r="B137" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>137209348</v>
       </c>
       <c r="B138" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>137209349</v>
       </c>
       <c r="B139" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>137209350</v>
       </c>
       <c r="B140" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>137209351</v>
       </c>
       <c r="B141" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>137209353</v>
       </c>
       <c r="B142" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>137209354</v>
       </c>
       <c r="B143" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>137209373</v>
       </c>
       <c r="B144" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>137209384</v>
       </c>
       <c r="B145" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>137209400</v>
       </c>
       <c r="B146" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>137209405</v>
       </c>
       <c r="B147" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>137237706</v>
       </c>
       <c r="B148" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>137237707</v>
       </c>
       <c r="B149" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>137237709</v>
       </c>
       <c r="B150" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>137237712</v>
       </c>
       <c r="B151" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137237713</v>
       </c>
       <c r="B152" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137237714</v>
       </c>
       <c r="B153" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137237715</v>
       </c>
       <c r="B154" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137237719</v>
       </c>
       <c r="B155" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>137237720</v>
       </c>
       <c r="B156" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>137237723</v>
       </c>
       <c r="B157" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137238613</v>
       </c>
       <c r="B158" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>137238614</v>
       </c>
       <c r="B159" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>137238616</v>
       </c>
       <c r="B160" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137238617</v>
       </c>
       <c r="B161" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>137238620</v>
       </c>
       <c r="B162" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>137238621</v>
       </c>
       <c r="B163" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>137238622</v>
       </c>
       <c r="B164" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>137238626</v>
       </c>
       <c r="B165" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>137238627</v>
       </c>
       <c r="B166" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>137238628</v>
       </c>
       <c r="B167" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>137238629</v>
       </c>
       <c r="B168" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>137238631</v>
       </c>
       <c r="B169" t="n">
-        <v>79501</v>
+        <v>79503</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>137199379</v>
       </c>
       <c r="B170" t="n">
-        <v>78904</v>
+        <v>78906</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>137199357</v>
       </c>
       <c r="B186" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>137199419</v>
       </c>
       <c r="B187" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>137237711</v>
       </c>
       <c r="B188" t="n">
-        <v>79258</v>
+        <v>79260</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>137199372</v>
       </c>
       <c r="B204" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>137199380</v>
       </c>
       <c r="B205" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>137199383</v>
       </c>
       <c r="B206" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>137199385</v>
       </c>
       <c r="B207" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>137199394</v>
       </c>
       <c r="B208" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>137199415</v>
       </c>
       <c r="B209" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>137209336</v>
       </c>
       <c r="B210" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>137209342</v>
       </c>
       <c r="B211" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>137209357</v>
       </c>
       <c r="B212" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>137209381</v>
       </c>
       <c r="B213" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>137209383</v>
       </c>
       <c r="B214" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>137209388</v>
       </c>
       <c r="B215" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>137209389</v>
       </c>
       <c r="B216" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>137209392</v>
       </c>
       <c r="B217" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>137209395</v>
       </c>
       <c r="B218" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>137209401</v>
       </c>
       <c r="B219" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>137209408</v>
       </c>
       <c r="B220" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>137209409</v>
       </c>
       <c r="B221" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>137237726</v>
       </c>
       <c r="B222" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>137238630</v>
       </c>
       <c r="B223" t="n">
-        <v>80120</v>
+        <v>80122</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>137199358</v>
       </c>
       <c r="B226" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25947,7 +25947,7 @@
         <v>137199362</v>
       </c>
       <c r="B227" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26064,7 +26064,7 @@
         <v>137199370</v>
       </c>
       <c r="B228" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26181,7 +26181,7 @@
         <v>137199371</v>
       </c>
       <c r="B229" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26298,7 +26298,7 @@
         <v>137199384</v>
       </c>
       <c r="B230" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26415,7 +26415,7 @@
         <v>137199399</v>
       </c>
       <c r="B231" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26532,7 +26532,7 @@
         <v>137199367</v>
       </c>
       <c r="B232" t="n">
-        <v>58021</v>
+        <v>58023</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26766,7 +26766,7 @@
         <v>137199332</v>
       </c>
       <c r="B234" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26883,7 +26883,7 @@
         <v>137199334</v>
       </c>
       <c r="B235" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -27000,7 +27000,7 @@
         <v>137199337</v>
       </c>
       <c r="B236" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27122,7 +27122,7 @@
         <v>137199350</v>
       </c>
       <c r="B237" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27244,7 +27244,7 @@
         <v>137199353</v>
       </c>
       <c r="B238" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27361,7 +27361,7 @@
         <v>137199355</v>
       </c>
       <c r="B239" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27478,7 +27478,7 @@
         <v>137199356</v>
       </c>
       <c r="B240" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27595,7 +27595,7 @@
         <v>137199376</v>
       </c>
       <c r="B241" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27712,7 +27712,7 @@
         <v>137199392</v>
       </c>
       <c r="B242" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27829,7 +27829,7 @@
         <v>137199393</v>
       </c>
       <c r="B243" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27946,7 +27946,7 @@
         <v>137199404</v>
       </c>
       <c r="B244" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -28063,7 +28063,7 @@
         <v>137199410</v>
       </c>
       <c r="B245" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28180,7 +28180,7 @@
         <v>137199411</v>
       </c>
       <c r="B246" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28297,7 +28297,7 @@
         <v>137209406</v>
       </c>
       <c r="B247" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28414,7 +28414,7 @@
         <v>137237721</v>
       </c>
       <c r="B248" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28531,7 +28531,7 @@
         <v>137237811</v>
       </c>
       <c r="B249" t="n">
-        <v>57208</v>
+        <v>57210</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28880,7 +28880,7 @@
         <v>137203501</v>
       </c>
       <c r="B252" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28992,7 +28992,7 @@
         <v>137238615</v>
       </c>
       <c r="B253" t="n">
-        <v>58182</v>
+        <v>58184</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29116,7 +29116,7 @@
         <v>137199361</v>
       </c>
       <c r="B254" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29233,7 +29233,7 @@
         <v>137199363</v>
       </c>
       <c r="B255" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29350,7 +29350,7 @@
         <v>137199412</v>
       </c>
       <c r="B256" t="n">
-        <v>8463</v>
+        <v>8464</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29467,7 +29467,7 @@
         <v>137199409</v>
       </c>
       <c r="B257" t="n">
-        <v>56585</v>
+        <v>56587</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32173,7 +32173,7 @@
         <v>137199397</v>
       </c>
       <c r="B280" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32294,7 +32294,7 @@
         <v>137209378</v>
       </c>
       <c r="B281" t="n">
-        <v>98257</v>
+        <v>98259</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137199338</v>
       </c>
       <c r="B284" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>137199381</v>
       </c>
       <c r="B285" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>137203492</v>
       </c>
       <c r="B286" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32961,7 +32961,7 @@
         <v>137209361</v>
       </c>
       <c r="B287" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>137209365</v>
       </c>
       <c r="B288" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33190,7 +33190,7 @@
         <v>137209390</v>
       </c>
       <c r="B289" t="n">
-        <v>98251</v>
+        <v>98253</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -36003,7 +36003,7 @@
         <v>137199414</v>
       </c>
       <c r="B315" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>137209363</v>
       </c>
       <c r="B316" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>137209374</v>
       </c>
       <c r="B317" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -36349,7 +36349,7 @@
         <v>137209379</v>
       </c>
       <c r="B318" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>137209386</v>
       </c>
       <c r="B319" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -36574,7 +36574,7 @@
         <v>137209407</v>
       </c>
       <c r="B320" t="n">
-        <v>79259</v>
+        <v>79261</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37125,7 +37125,7 @@
         <v>137199418</v>
       </c>
       <c r="B325" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>137209385</v>
       </c>
       <c r="B326" t="n">
-        <v>80091</v>
+        <v>80093</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -37359,7 +37359,7 @@
         <v>137199400</v>
       </c>
       <c r="B327" t="n">
-        <v>79524</v>
+        <v>79526</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -25856,11 +25856,7 @@
         </is>
       </c>
       <c r="I226" t="inlineStr"/>
-      <c r="M226" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M226" t="inlineStr"/>
       <c r="P226" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -25973,11 +25969,7 @@
         </is>
       </c>
       <c r="I227" t="inlineStr"/>
-      <c r="M227" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M227" t="inlineStr"/>
       <c r="P227" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -26090,11 +26082,7 @@
         </is>
       </c>
       <c r="I228" t="inlineStr"/>
-      <c r="M228" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M228" t="inlineStr"/>
       <c r="P228" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -26207,11 +26195,7 @@
         </is>
       </c>
       <c r="I229" t="inlineStr"/>
-      <c r="M229" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M229" t="inlineStr"/>
       <c r="P229" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -26324,11 +26308,7 @@
         </is>
       </c>
       <c r="I230" t="inlineStr"/>
-      <c r="M230" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M230" t="inlineStr"/>
       <c r="P230" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -26441,11 +26421,7 @@
         </is>
       </c>
       <c r="I231" t="inlineStr"/>
-      <c r="M231" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M231" t="inlineStr"/>
       <c r="P231" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -26558,11 +26534,7 @@
         </is>
       </c>
       <c r="I232" t="inlineStr"/>
-      <c r="M232" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M232" t="inlineStr"/>
       <c r="P232" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -26792,11 +26764,7 @@
         </is>
       </c>
       <c r="I234" t="inlineStr"/>
-      <c r="M234" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M234" t="inlineStr"/>
       <c r="P234" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -26909,11 +26877,7 @@
         </is>
       </c>
       <c r="I235" t="inlineStr"/>
-      <c r="M235" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M235" t="inlineStr"/>
       <c r="P235" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -27026,16 +26990,8 @@
         </is>
       </c>
       <c r="I236" t="inlineStr"/>
-      <c r="L236" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M236" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L236" t="inlineStr"/>
+      <c r="M236" t="inlineStr"/>
       <c r="P236" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -27148,16 +27104,8 @@
         </is>
       </c>
       <c r="I237" t="inlineStr"/>
-      <c r="L237" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M237" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="L237" t="inlineStr"/>
+      <c r="M237" t="inlineStr"/>
       <c r="P237" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -27270,11 +27218,7 @@
         </is>
       </c>
       <c r="I238" t="inlineStr"/>
-      <c r="M238" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M238" t="inlineStr"/>
       <c r="P238" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -27387,11 +27331,7 @@
         </is>
       </c>
       <c r="I239" t="inlineStr"/>
-      <c r="M239" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M239" t="inlineStr"/>
       <c r="P239" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -27504,11 +27444,7 @@
         </is>
       </c>
       <c r="I240" t="inlineStr"/>
-      <c r="M240" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M240" t="inlineStr"/>
       <c r="P240" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -27621,11 +27557,7 @@
         </is>
       </c>
       <c r="I241" t="inlineStr"/>
-      <c r="M241" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M241" t="inlineStr"/>
       <c r="P241" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -27738,11 +27670,7 @@
         </is>
       </c>
       <c r="I242" t="inlineStr"/>
-      <c r="M242" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="M242" t="inlineStr"/>
       <c r="P242" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -27855,11 +27783,7 @@
         </is>
       </c>
       <c r="I243" t="inlineStr"/>
-      <c r="M243" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M243" t="inlineStr"/>
       <c r="P243" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -27972,11 +27896,7 @@
         </is>
       </c>
       <c r="I244" t="inlineStr"/>
-      <c r="M244" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M244" t="inlineStr"/>
       <c r="P244" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -28089,11 +28009,7 @@
         </is>
       </c>
       <c r="I245" t="inlineStr"/>
-      <c r="M245" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="M245" t="inlineStr"/>
       <c r="P245" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -28206,11 +28122,7 @@
         </is>
       </c>
       <c r="I246" t="inlineStr"/>
-      <c r="M246" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M246" t="inlineStr"/>
       <c r="P246" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -28559,11 +28471,7 @@
       <c r="I249" t="inlineStr"/>
       <c r="K249" t="inlineStr"/>
       <c r="L249" t="inlineStr"/>
-      <c r="M249" t="inlineStr">
-        <is>
-          <t>äldre spillning</t>
-        </is>
-      </c>
+      <c r="M249" t="inlineStr"/>
       <c r="N249" t="inlineStr"/>
       <c r="P249" t="inlineStr">
         <is>
@@ -29024,11 +28932,7 @@
       </c>
       <c r="K253" t="inlineStr"/>
       <c r="L253" t="inlineStr"/>
-      <c r="M253" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
+      <c r="M253" t="inlineStr"/>
       <c r="N253" t="inlineStr"/>
       <c r="P253" t="inlineStr">
         <is>
@@ -29142,11 +29046,7 @@
         </is>
       </c>
       <c r="I254" t="inlineStr"/>
-      <c r="M254" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M254" t="inlineStr"/>
       <c r="P254" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -29259,11 +29159,7 @@
         </is>
       </c>
       <c r="I255" t="inlineStr"/>
-      <c r="M255" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M255" t="inlineStr"/>
       <c r="P255" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -29376,11 +29272,7 @@
         </is>
       </c>
       <c r="I256" t="inlineStr"/>
-      <c r="M256" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+      <c r="M256" t="inlineStr"/>
       <c r="P256" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>
@@ -29493,11 +29385,7 @@
         </is>
       </c>
       <c r="I257" t="inlineStr"/>
-      <c r="M257" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
+      <c r="M257" t="inlineStr"/>
       <c r="P257" t="inlineStr">
         <is>
           <t>Skrollhuvud, Dlr</t>

--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -1380,7 +1380,7 @@
         <v>137199339</v>
       </c>
       <c r="B8" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137199388</v>
       </c>
       <c r="B9" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137199417</v>
       </c>
       <c r="B10" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137203503</v>
       </c>
       <c r="B11" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>137237700</v>
       </c>
       <c r="B12" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>137237702</v>
       </c>
       <c r="B13" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>137237725</v>
       </c>
       <c r="B14" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137238609</v>
       </c>
       <c r="B15" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137238619</v>
       </c>
       <c r="B16" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137238623</v>
       </c>
       <c r="B17" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>137238624</v>
       </c>
       <c r="B18" t="n">
-        <v>93442</v>
+        <v>93445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137199403</v>
       </c>
       <c r="B19" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137199406</v>
       </c>
       <c r="B20" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137199408</v>
       </c>
       <c r="B21" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137237704</v>
       </c>
       <c r="B22" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>137237705</v>
       </c>
       <c r="B23" t="n">
-        <v>92166</v>
+        <v>92169</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137199347</v>
       </c>
       <c r="B24" t="n">
-        <v>93468</v>
+        <v>93471</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>137199397</v>
       </c>
       <c r="B280" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>137209378</v>
       </c>
       <c r="B281" t="n">
-        <v>98259</v>
+        <v>98262</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>137199338</v>
       </c>
       <c r="B284" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137199381</v>
       </c>
       <c r="B285" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>137203492</v>
       </c>
       <c r="B286" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>137209361</v>
       </c>
       <c r="B287" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>137209365</v>
       </c>
       <c r="B288" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>137209390</v>
       </c>
       <c r="B289" t="n">
-        <v>98253</v>
+        <v>98256</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>

--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199346</v>
       </c>
       <c r="B2" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>137199349</v>
       </c>
       <c r="B3" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137209347</v>
       </c>
       <c r="B4" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137209391</v>
       </c>
       <c r="B5" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>137237701</v>
       </c>
       <c r="B6" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137237728</v>
       </c>
       <c r="B7" t="n">
-        <v>79169</v>
+        <v>79179</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137199339</v>
       </c>
       <c r="B8" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137199388</v>
       </c>
       <c r="B9" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137199417</v>
       </c>
       <c r="B10" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137203503</v>
       </c>
       <c r="B11" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>137237700</v>
       </c>
       <c r="B12" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>137237702</v>
       </c>
       <c r="B13" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>137237725</v>
       </c>
       <c r="B14" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137238609</v>
       </c>
       <c r="B15" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137238619</v>
       </c>
       <c r="B16" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137238623</v>
       </c>
       <c r="B17" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>137238624</v>
       </c>
       <c r="B18" t="n">
-        <v>93445</v>
+        <v>93455</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137199403</v>
       </c>
       <c r="B19" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137199406</v>
       </c>
       <c r="B20" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137199408</v>
       </c>
       <c r="B21" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137237704</v>
       </c>
       <c r="B22" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>137237705</v>
       </c>
       <c r="B23" t="n">
-        <v>92169</v>
+        <v>92179</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137199347</v>
       </c>
       <c r="B24" t="n">
-        <v>93471</v>
+        <v>93481</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>137199336</v>
       </c>
       <c r="B96" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>137199341</v>
       </c>
       <c r="B97" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>137199342</v>
       </c>
       <c r="B98" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>137199343</v>
       </c>
       <c r="B99" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>137199351</v>
       </c>
       <c r="B100" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>137199354</v>
       </c>
       <c r="B101" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>137199359</v>
       </c>
       <c r="B102" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>137199360</v>
       </c>
       <c r="B103" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>137199364</v>
       </c>
       <c r="B104" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>137199365</v>
       </c>
       <c r="B105" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>137199378</v>
       </c>
       <c r="B106" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>137199382</v>
       </c>
       <c r="B107" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>137199386</v>
       </c>
       <c r="B108" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>137199387</v>
       </c>
       <c r="B109" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>137199389</v>
       </c>
       <c r="B110" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>137199390</v>
       </c>
       <c r="B111" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>137199395</v>
       </c>
       <c r="B112" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>137199401</v>
       </c>
       <c r="B113" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>137199407</v>
       </c>
       <c r="B114" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>137199416</v>
       </c>
       <c r="B115" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>137199420</v>
       </c>
       <c r="B116" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>137203487</v>
       </c>
       <c r="B117" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>137203488</v>
       </c>
       <c r="B118" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>137203490</v>
       </c>
       <c r="B119" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>137203491</v>
       </c>
       <c r="B120" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>137203493</v>
       </c>
       <c r="B121" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>137203494</v>
       </c>
       <c r="B122" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>137203496</v>
       </c>
       <c r="B123" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>137203502</v>
       </c>
       <c r="B124" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>137203504</v>
       </c>
       <c r="B125" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>137203505</v>
       </c>
       <c r="B126" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>137203506</v>
       </c>
       <c r="B127" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>137203507</v>
       </c>
       <c r="B128" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>137203508</v>
       </c>
       <c r="B129" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>137203509</v>
       </c>
       <c r="B130" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>137203510</v>
       </c>
       <c r="B131" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>137203511</v>
       </c>
       <c r="B132" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>137203512</v>
       </c>
       <c r="B133" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>137203513</v>
       </c>
       <c r="B134" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>137203514</v>
       </c>
       <c r="B135" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>137203515</v>
       </c>
       <c r="B136" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>137209346</v>
       </c>
       <c r="B137" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>137209348</v>
       </c>
       <c r="B138" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>137209349</v>
       </c>
       <c r="B139" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>137209350</v>
       </c>
       <c r="B140" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>137209351</v>
       </c>
       <c r="B141" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>137209353</v>
       </c>
       <c r="B142" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>137209354</v>
       </c>
       <c r="B143" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>137209373</v>
       </c>
       <c r="B144" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>137209384</v>
       </c>
       <c r="B145" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>137209400</v>
       </c>
       <c r="B146" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>137209405</v>
       </c>
       <c r="B147" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>137237706</v>
       </c>
       <c r="B148" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>137237707</v>
       </c>
       <c r="B149" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>137237709</v>
       </c>
       <c r="B150" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>137237712</v>
       </c>
       <c r="B151" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137237713</v>
       </c>
       <c r="B152" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137237714</v>
       </c>
       <c r="B153" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137237715</v>
       </c>
       <c r="B154" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137237719</v>
       </c>
       <c r="B155" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>137237720</v>
       </c>
       <c r="B156" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>137237723</v>
       </c>
       <c r="B157" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137238613</v>
       </c>
       <c r="B158" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>137238614</v>
       </c>
       <c r="B159" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>137238616</v>
       </c>
       <c r="B160" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137238617</v>
       </c>
       <c r="B161" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>137238620</v>
       </c>
       <c r="B162" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>137238621</v>
       </c>
       <c r="B163" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>137238622</v>
       </c>
       <c r="B164" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>137238626</v>
       </c>
       <c r="B165" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>137238627</v>
       </c>
       <c r="B166" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>137238628</v>
       </c>
       <c r="B167" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>137238629</v>
       </c>
       <c r="B168" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>137238631</v>
       </c>
       <c r="B169" t="n">
-        <v>79503</v>
+        <v>79513</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>137199379</v>
       </c>
       <c r="B170" t="n">
-        <v>78906</v>
+        <v>78916</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>137199357</v>
       </c>
       <c r="B186" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>137199419</v>
       </c>
       <c r="B187" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>137237711</v>
       </c>
       <c r="B188" t="n">
-        <v>79260</v>
+        <v>79270</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>137199372</v>
       </c>
       <c r="B204" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>137199380</v>
       </c>
       <c r="B205" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>137199383</v>
       </c>
       <c r="B206" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>137199385</v>
       </c>
       <c r="B207" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>137199394</v>
       </c>
       <c r="B208" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>137199415</v>
       </c>
       <c r="B209" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>137209336</v>
       </c>
       <c r="B210" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>137209342</v>
       </c>
       <c r="B211" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>137209357</v>
       </c>
       <c r="B212" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>137209381</v>
       </c>
       <c r="B213" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>137209383</v>
       </c>
       <c r="B214" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>137209388</v>
       </c>
       <c r="B215" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>137209389</v>
       </c>
       <c r="B216" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>137209392</v>
       </c>
       <c r="B217" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>137209395</v>
       </c>
       <c r="B218" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>137209401</v>
       </c>
       <c r="B219" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>137209408</v>
       </c>
       <c r="B220" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>137209409</v>
       </c>
       <c r="B221" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>137237726</v>
       </c>
       <c r="B222" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>137238630</v>
       </c>
       <c r="B223" t="n">
-        <v>80122</v>
+        <v>80132</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>137199358</v>
       </c>
       <c r="B226" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>137199362</v>
       </c>
       <c r="B227" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>137199370</v>
       </c>
       <c r="B228" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>137199371</v>
       </c>
       <c r="B229" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>137199384</v>
       </c>
       <c r="B230" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>137199399</v>
       </c>
       <c r="B231" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>137199367</v>
       </c>
       <c r="B232" t="n">
-        <v>58023</v>
+        <v>58033</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>137199332</v>
       </c>
       <c r="B234" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>137199334</v>
       </c>
       <c r="B235" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>137199337</v>
       </c>
       <c r="B236" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>137199350</v>
       </c>
       <c r="B237" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>137199353</v>
       </c>
       <c r="B238" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>137199355</v>
       </c>
       <c r="B239" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>137199356</v>
       </c>
       <c r="B240" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>137199376</v>
       </c>
       <c r="B241" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>137199392</v>
       </c>
       <c r="B242" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>137199393</v>
       </c>
       <c r="B243" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>137199404</v>
       </c>
       <c r="B244" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>137199410</v>
       </c>
       <c r="B245" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>137199411</v>
       </c>
       <c r="B246" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>137209406</v>
       </c>
       <c r="B247" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>137237721</v>
       </c>
       <c r="B248" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>137237811</v>
       </c>
       <c r="B249" t="n">
-        <v>57210</v>
+        <v>57220</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>137203501</v>
       </c>
       <c r="B252" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>137238615</v>
       </c>
       <c r="B253" t="n">
-        <v>58184</v>
+        <v>58194</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29020,7 +29020,7 @@
         <v>137199361</v>
       </c>
       <c r="B254" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -29133,7 +29133,7 @@
         <v>137199363</v>
       </c>
       <c r="B255" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -29246,7 +29246,7 @@
         <v>137199412</v>
       </c>
       <c r="B256" t="n">
-        <v>8464</v>
+        <v>8470</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>137199409</v>
       </c>
       <c r="B257" t="n">
-        <v>56587</v>
+        <v>56597</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>137199397</v>
       </c>
       <c r="B280" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>137209378</v>
       </c>
       <c r="B281" t="n">
-        <v>98262</v>
+        <v>98272</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>137199338</v>
       </c>
       <c r="B284" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137199381</v>
       </c>
       <c r="B285" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>137203492</v>
       </c>
       <c r="B286" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>137209361</v>
       </c>
       <c r="B287" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>137209365</v>
       </c>
       <c r="B288" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>137209390</v>
       </c>
       <c r="B289" t="n">
-        <v>98256</v>
+        <v>98266</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>137199414</v>
       </c>
       <c r="B315" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>137209363</v>
       </c>
       <c r="B316" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>137209374</v>
       </c>
       <c r="B317" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>137209379</v>
       </c>
       <c r="B318" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>137209386</v>
       </c>
       <c r="B319" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>137209407</v>
       </c>
       <c r="B320" t="n">
-        <v>79261</v>
+        <v>79271</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>137199418</v>
       </c>
       <c r="B325" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>137209385</v>
       </c>
       <c r="B326" t="n">
-        <v>80093</v>
+        <v>80103</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>137199400</v>
       </c>
       <c r="B327" t="n">
-        <v>79526</v>
+        <v>79536</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -1380,7 +1380,7 @@
         <v>137199339</v>
       </c>
       <c r="B8" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137199388</v>
       </c>
       <c r="B9" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137199417</v>
       </c>
       <c r="B10" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137203503</v>
       </c>
       <c r="B11" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>137237700</v>
       </c>
       <c r="B12" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>137237702</v>
       </c>
       <c r="B13" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>137237725</v>
       </c>
       <c r="B14" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137238609</v>
       </c>
       <c r="B15" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137238619</v>
       </c>
       <c r="B16" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137238623</v>
       </c>
       <c r="B17" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>137238624</v>
       </c>
       <c r="B18" t="n">
-        <v>93455</v>
+        <v>93456</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137199403</v>
       </c>
       <c r="B19" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137199406</v>
       </c>
       <c r="B20" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137199408</v>
       </c>
       <c r="B21" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137237704</v>
       </c>
       <c r="B22" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>137237705</v>
       </c>
       <c r="B23" t="n">
-        <v>92179</v>
+        <v>92180</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137199347</v>
       </c>
       <c r="B24" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>137199397</v>
       </c>
       <c r="B280" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>137209378</v>
       </c>
       <c r="B281" t="n">
-        <v>98272</v>
+        <v>98273</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>137199338</v>
       </c>
       <c r="B284" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137199381</v>
       </c>
       <c r="B285" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>137203492</v>
       </c>
       <c r="B286" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>137209361</v>
       </c>
       <c r="B287" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>137209365</v>
       </c>
       <c r="B288" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>137209390</v>
       </c>
       <c r="B289" t="n">
-        <v>98266</v>
+        <v>98267</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>

--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199346</v>
       </c>
       <c r="B2" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>137199349</v>
       </c>
       <c r="B3" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137209347</v>
       </c>
       <c r="B4" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137209391</v>
       </c>
       <c r="B5" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>137237701</v>
       </c>
       <c r="B6" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137237728</v>
       </c>
       <c r="B7" t="n">
-        <v>79179</v>
+        <v>79182</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137199339</v>
       </c>
       <c r="B8" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137199388</v>
       </c>
       <c r="B9" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137199417</v>
       </c>
       <c r="B10" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137203503</v>
       </c>
       <c r="B11" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>137237700</v>
       </c>
       <c r="B12" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>137237702</v>
       </c>
       <c r="B13" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>137237725</v>
       </c>
       <c r="B14" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137238609</v>
       </c>
       <c r="B15" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137238619</v>
       </c>
       <c r="B16" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137238623</v>
       </c>
       <c r="B17" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>137238624</v>
       </c>
       <c r="B18" t="n">
-        <v>93456</v>
+        <v>93461</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137199403</v>
       </c>
       <c r="B19" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137199406</v>
       </c>
       <c r="B20" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137199408</v>
       </c>
       <c r="B21" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137237704</v>
       </c>
       <c r="B22" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>137237705</v>
       </c>
       <c r="B23" t="n">
-        <v>92180</v>
+        <v>92183</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137199347</v>
       </c>
       <c r="B24" t="n">
-        <v>93482</v>
+        <v>93487</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>137199336</v>
       </c>
       <c r="B96" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>137199341</v>
       </c>
       <c r="B97" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>137199342</v>
       </c>
       <c r="B98" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>137199343</v>
       </c>
       <c r="B99" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>137199351</v>
       </c>
       <c r="B100" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>137199354</v>
       </c>
       <c r="B101" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>137199359</v>
       </c>
       <c r="B102" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>137199360</v>
       </c>
       <c r="B103" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>137199364</v>
       </c>
       <c r="B104" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>137199365</v>
       </c>
       <c r="B105" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>137199378</v>
       </c>
       <c r="B106" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>137199382</v>
       </c>
       <c r="B107" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>137199386</v>
       </c>
       <c r="B108" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>137199387</v>
       </c>
       <c r="B109" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>137199389</v>
       </c>
       <c r="B110" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>137199390</v>
       </c>
       <c r="B111" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>137199395</v>
       </c>
       <c r="B112" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>137199401</v>
       </c>
       <c r="B113" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>137199407</v>
       </c>
       <c r="B114" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>137199416</v>
       </c>
       <c r="B115" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>137199420</v>
       </c>
       <c r="B116" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>137203487</v>
       </c>
       <c r="B117" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>137203488</v>
       </c>
       <c r="B118" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>137203490</v>
       </c>
       <c r="B119" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>137203491</v>
       </c>
       <c r="B120" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>137203493</v>
       </c>
       <c r="B121" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>137203494</v>
       </c>
       <c r="B122" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>137203496</v>
       </c>
       <c r="B123" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>137203502</v>
       </c>
       <c r="B124" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>137203504</v>
       </c>
       <c r="B125" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>137203505</v>
       </c>
       <c r="B126" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>137203506</v>
       </c>
       <c r="B127" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>137203507</v>
       </c>
       <c r="B128" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>137203508</v>
       </c>
       <c r="B129" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>137203509</v>
       </c>
       <c r="B130" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>137203510</v>
       </c>
       <c r="B131" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>137203511</v>
       </c>
       <c r="B132" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>137203512</v>
       </c>
       <c r="B133" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>137203513</v>
       </c>
       <c r="B134" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>137203514</v>
       </c>
       <c r="B135" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>137203515</v>
       </c>
       <c r="B136" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>137209346</v>
       </c>
       <c r="B137" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>137209348</v>
       </c>
       <c r="B138" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>137209349</v>
       </c>
       <c r="B139" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>137209350</v>
       </c>
       <c r="B140" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>137209351</v>
       </c>
       <c r="B141" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>137209353</v>
       </c>
       <c r="B142" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>137209354</v>
       </c>
       <c r="B143" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>137209373</v>
       </c>
       <c r="B144" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>137209384</v>
       </c>
       <c r="B145" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>137209400</v>
       </c>
       <c r="B146" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>137209405</v>
       </c>
       <c r="B147" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>137237706</v>
       </c>
       <c r="B148" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>137237707</v>
       </c>
       <c r="B149" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>137237709</v>
       </c>
       <c r="B150" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>137237712</v>
       </c>
       <c r="B151" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137237713</v>
       </c>
       <c r="B152" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137237714</v>
       </c>
       <c r="B153" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137237715</v>
       </c>
       <c r="B154" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137237719</v>
       </c>
       <c r="B155" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>137237720</v>
       </c>
       <c r="B156" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>137237723</v>
       </c>
       <c r="B157" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137238613</v>
       </c>
       <c r="B158" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>137238614</v>
       </c>
       <c r="B159" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>137238616</v>
       </c>
       <c r="B160" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137238617</v>
       </c>
       <c r="B161" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>137238620</v>
       </c>
       <c r="B162" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>137238621</v>
       </c>
       <c r="B163" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>137238622</v>
       </c>
       <c r="B164" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>137238626</v>
       </c>
       <c r="B165" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>137238627</v>
       </c>
       <c r="B166" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>137238628</v>
       </c>
       <c r="B167" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>137238629</v>
       </c>
       <c r="B168" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>137238631</v>
       </c>
       <c r="B169" t="n">
-        <v>79513</v>
+        <v>79516</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>137199379</v>
       </c>
       <c r="B170" t="n">
-        <v>78916</v>
+        <v>78919</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>137199357</v>
       </c>
       <c r="B186" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>137199419</v>
       </c>
       <c r="B187" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>137237711</v>
       </c>
       <c r="B188" t="n">
-        <v>79270</v>
+        <v>79273</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>137199372</v>
       </c>
       <c r="B204" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>137199380</v>
       </c>
       <c r="B205" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>137199383</v>
       </c>
       <c r="B206" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>137199385</v>
       </c>
       <c r="B207" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>137199394</v>
       </c>
       <c r="B208" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>137199415</v>
       </c>
       <c r="B209" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>137209336</v>
       </c>
       <c r="B210" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>137209342</v>
       </c>
       <c r="B211" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>137209357</v>
       </c>
       <c r="B212" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>137209381</v>
       </c>
       <c r="B213" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>137209383</v>
       </c>
       <c r="B214" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>137209388</v>
       </c>
       <c r="B215" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>137209389</v>
       </c>
       <c r="B216" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>137209392</v>
       </c>
       <c r="B217" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>137209395</v>
       </c>
       <c r="B218" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>137209401</v>
       </c>
       <c r="B219" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>137209408</v>
       </c>
       <c r="B220" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>137209409</v>
       </c>
       <c r="B221" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>137237726</v>
       </c>
       <c r="B222" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>137238630</v>
       </c>
       <c r="B223" t="n">
-        <v>80132</v>
+        <v>80135</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>137199358</v>
       </c>
       <c r="B226" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>137199362</v>
       </c>
       <c r="B227" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>137199370</v>
       </c>
       <c r="B228" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>137199371</v>
       </c>
       <c r="B229" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>137199384</v>
       </c>
       <c r="B230" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>137199399</v>
       </c>
       <c r="B231" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>137199367</v>
       </c>
       <c r="B232" t="n">
-        <v>58033</v>
+        <v>58034</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>137199332</v>
       </c>
       <c r="B234" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>137199334</v>
       </c>
       <c r="B235" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>137199337</v>
       </c>
       <c r="B236" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>137199350</v>
       </c>
       <c r="B237" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>137199353</v>
       </c>
       <c r="B238" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>137199355</v>
       </c>
       <c r="B239" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>137199356</v>
       </c>
       <c r="B240" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>137199376</v>
       </c>
       <c r="B241" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>137199392</v>
       </c>
       <c r="B242" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>137199393</v>
       </c>
       <c r="B243" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>137199404</v>
       </c>
       <c r="B244" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>137199410</v>
       </c>
       <c r="B245" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>137199411</v>
       </c>
       <c r="B246" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>137209406</v>
       </c>
       <c r="B247" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>137237721</v>
       </c>
       <c r="B248" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>137237811</v>
       </c>
       <c r="B249" t="n">
-        <v>57220</v>
+        <v>57221</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>137203501</v>
       </c>
       <c r="B252" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>137238615</v>
       </c>
       <c r="B253" t="n">
-        <v>58194</v>
+        <v>58195</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>137199409</v>
       </c>
       <c r="B257" t="n">
-        <v>56597</v>
+        <v>56598</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>137199397</v>
       </c>
       <c r="B280" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>137209378</v>
       </c>
       <c r="B281" t="n">
-        <v>98273</v>
+        <v>98278</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>137199338</v>
       </c>
       <c r="B284" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137199381</v>
       </c>
       <c r="B285" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>137203492</v>
       </c>
       <c r="B286" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>137209361</v>
       </c>
       <c r="B287" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>137209365</v>
       </c>
       <c r="B288" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>137209390</v>
       </c>
       <c r="B289" t="n">
-        <v>98267</v>
+        <v>98272</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>137199414</v>
       </c>
       <c r="B315" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>137209363</v>
       </c>
       <c r="B316" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>137209374</v>
       </c>
       <c r="B317" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>137209379</v>
       </c>
       <c r="B318" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>137209386</v>
       </c>
       <c r="B319" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>137209407</v>
       </c>
       <c r="B320" t="n">
-        <v>79271</v>
+        <v>79274</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>137199418</v>
       </c>
       <c r="B325" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>137209385</v>
       </c>
       <c r="B326" t="n">
-        <v>80103</v>
+        <v>80106</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>137199400</v>
       </c>
       <c r="B327" t="n">
-        <v>79536</v>
+        <v>79539</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -1380,7 +1380,7 @@
         <v>137199339</v>
       </c>
       <c r="B8" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137199388</v>
       </c>
       <c r="B9" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137199417</v>
       </c>
       <c r="B10" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137203503</v>
       </c>
       <c r="B11" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>137237700</v>
       </c>
       <c r="B12" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>137237702</v>
       </c>
       <c r="B13" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>137237725</v>
       </c>
       <c r="B14" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137238609</v>
       </c>
       <c r="B15" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137238619</v>
       </c>
       <c r="B16" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137238623</v>
       </c>
       <c r="B17" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>137238624</v>
       </c>
       <c r="B18" t="n">
-        <v>93461</v>
+        <v>93463</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137199403</v>
       </c>
       <c r="B19" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137199406</v>
       </c>
       <c r="B20" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137199408</v>
       </c>
       <c r="B21" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137237704</v>
       </c>
       <c r="B22" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>137237705</v>
       </c>
       <c r="B23" t="n">
-        <v>92183</v>
+        <v>92185</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137199347</v>
       </c>
       <c r="B24" t="n">
-        <v>93487</v>
+        <v>93489</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>137199397</v>
       </c>
       <c r="B280" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>137209378</v>
       </c>
       <c r="B281" t="n">
-        <v>98278</v>
+        <v>98280</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>137199338</v>
       </c>
       <c r="B284" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137199381</v>
       </c>
       <c r="B285" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>137203492</v>
       </c>
       <c r="B286" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>137209361</v>
       </c>
       <c r="B287" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>137209365</v>
       </c>
       <c r="B288" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>137209390</v>
       </c>
       <c r="B289" t="n">
-        <v>98272</v>
+        <v>98274</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>

--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199346</v>
       </c>
       <c r="B2" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>137199349</v>
       </c>
       <c r="B3" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137209347</v>
       </c>
       <c r="B4" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137209391</v>
       </c>
       <c r="B5" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>137237701</v>
       </c>
       <c r="B6" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137237728</v>
       </c>
       <c r="B7" t="n">
-        <v>79182</v>
+        <v>79187</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137199339</v>
       </c>
       <c r="B8" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137199388</v>
       </c>
       <c r="B9" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137199417</v>
       </c>
       <c r="B10" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137203503</v>
       </c>
       <c r="B11" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>137237700</v>
       </c>
       <c r="B12" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>137237702</v>
       </c>
       <c r="B13" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>137237725</v>
       </c>
       <c r="B14" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137238609</v>
       </c>
       <c r="B15" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137238619</v>
       </c>
       <c r="B16" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137238623</v>
       </c>
       <c r="B17" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>137238624</v>
       </c>
       <c r="B18" t="n">
-        <v>93463</v>
+        <v>93469</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137199403</v>
       </c>
       <c r="B19" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137199406</v>
       </c>
       <c r="B20" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137199408</v>
       </c>
       <c r="B21" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137237704</v>
       </c>
       <c r="B22" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>137237705</v>
       </c>
       <c r="B23" t="n">
-        <v>92185</v>
+        <v>92190</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137199347</v>
       </c>
       <c r="B24" t="n">
-        <v>93489</v>
+        <v>93495</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>137199336</v>
       </c>
       <c r="B96" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>137199341</v>
       </c>
       <c r="B97" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>137199342</v>
       </c>
       <c r="B98" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>137199343</v>
       </c>
       <c r="B99" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>137199351</v>
       </c>
       <c r="B100" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>137199354</v>
       </c>
       <c r="B101" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>137199359</v>
       </c>
       <c r="B102" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>137199360</v>
       </c>
       <c r="B103" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>137199364</v>
       </c>
       <c r="B104" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>137199365</v>
       </c>
       <c r="B105" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>137199378</v>
       </c>
       <c r="B106" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>137199382</v>
       </c>
       <c r="B107" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>137199386</v>
       </c>
       <c r="B108" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>137199387</v>
       </c>
       <c r="B109" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>137199389</v>
       </c>
       <c r="B110" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>137199390</v>
       </c>
       <c r="B111" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>137199395</v>
       </c>
       <c r="B112" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>137199401</v>
       </c>
       <c r="B113" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>137199407</v>
       </c>
       <c r="B114" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>137199416</v>
       </c>
       <c r="B115" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>137199420</v>
       </c>
       <c r="B116" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>137203487</v>
       </c>
       <c r="B117" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>137203488</v>
       </c>
       <c r="B118" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>137203490</v>
       </c>
       <c r="B119" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>137203491</v>
       </c>
       <c r="B120" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>137203493</v>
       </c>
       <c r="B121" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>137203494</v>
       </c>
       <c r="B122" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>137203496</v>
       </c>
       <c r="B123" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>137203502</v>
       </c>
       <c r="B124" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>137203504</v>
       </c>
       <c r="B125" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>137203505</v>
       </c>
       <c r="B126" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>137203506</v>
       </c>
       <c r="B127" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>137203507</v>
       </c>
       <c r="B128" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>137203508</v>
       </c>
       <c r="B129" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>137203509</v>
       </c>
       <c r="B130" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>137203510</v>
       </c>
       <c r="B131" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>137203511</v>
       </c>
       <c r="B132" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>137203512</v>
       </c>
       <c r="B133" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>137203513</v>
       </c>
       <c r="B134" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>137203514</v>
       </c>
       <c r="B135" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>137203515</v>
       </c>
       <c r="B136" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>137209346</v>
       </c>
       <c r="B137" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>137209348</v>
       </c>
       <c r="B138" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>137209349</v>
       </c>
       <c r="B139" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>137209350</v>
       </c>
       <c r="B140" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>137209351</v>
       </c>
       <c r="B141" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>137209353</v>
       </c>
       <c r="B142" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>137209354</v>
       </c>
       <c r="B143" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>137209373</v>
       </c>
       <c r="B144" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>137209384</v>
       </c>
       <c r="B145" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>137209400</v>
       </c>
       <c r="B146" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>137209405</v>
       </c>
       <c r="B147" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>137237706</v>
       </c>
       <c r="B148" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>137237707</v>
       </c>
       <c r="B149" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>137237709</v>
       </c>
       <c r="B150" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>137237712</v>
       </c>
       <c r="B151" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137237713</v>
       </c>
       <c r="B152" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137237714</v>
       </c>
       <c r="B153" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137237715</v>
       </c>
       <c r="B154" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137237719</v>
       </c>
       <c r="B155" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>137237720</v>
       </c>
       <c r="B156" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>137237723</v>
       </c>
       <c r="B157" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137238613</v>
       </c>
       <c r="B158" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>137238614</v>
       </c>
       <c r="B159" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>137238616</v>
       </c>
       <c r="B160" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137238617</v>
       </c>
       <c r="B161" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>137238620</v>
       </c>
       <c r="B162" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>137238621</v>
       </c>
       <c r="B163" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>137238622</v>
       </c>
       <c r="B164" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>137238626</v>
       </c>
       <c r="B165" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>137238627</v>
       </c>
       <c r="B166" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>137238628</v>
       </c>
       <c r="B167" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>137238629</v>
       </c>
       <c r="B168" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>137238631</v>
       </c>
       <c r="B169" t="n">
-        <v>79516</v>
+        <v>79521</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>137199379</v>
       </c>
       <c r="B170" t="n">
-        <v>78919</v>
+        <v>78924</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>137199357</v>
       </c>
       <c r="B186" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>137199419</v>
       </c>
       <c r="B187" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>137237711</v>
       </c>
       <c r="B188" t="n">
-        <v>79273</v>
+        <v>79278</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>137199372</v>
       </c>
       <c r="B204" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>137199380</v>
       </c>
       <c r="B205" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>137199383</v>
       </c>
       <c r="B206" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>137199385</v>
       </c>
       <c r="B207" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>137199394</v>
       </c>
       <c r="B208" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>137199415</v>
       </c>
       <c r="B209" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>137209336</v>
       </c>
       <c r="B210" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>137209342</v>
       </c>
       <c r="B211" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>137209357</v>
       </c>
       <c r="B212" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>137209381</v>
       </c>
       <c r="B213" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>137209383</v>
       </c>
       <c r="B214" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>137209388</v>
       </c>
       <c r="B215" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>137209389</v>
       </c>
       <c r="B216" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>137209392</v>
       </c>
       <c r="B217" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>137209395</v>
       </c>
       <c r="B218" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>137209401</v>
       </c>
       <c r="B219" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>137209408</v>
       </c>
       <c r="B220" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>137209409</v>
       </c>
       <c r="B221" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>137237726</v>
       </c>
       <c r="B222" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>137238630</v>
       </c>
       <c r="B223" t="n">
-        <v>80135</v>
+        <v>80140</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>137199358</v>
       </c>
       <c r="B226" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>137199362</v>
       </c>
       <c r="B227" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>137199370</v>
       </c>
       <c r="B228" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>137199371</v>
       </c>
       <c r="B229" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>137199384</v>
       </c>
       <c r="B230" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>137199399</v>
       </c>
       <c r="B231" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>137199367</v>
       </c>
       <c r="B232" t="n">
-        <v>58034</v>
+        <v>58035</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>137203501</v>
       </c>
       <c r="B252" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>137238615</v>
       </c>
       <c r="B253" t="n">
-        <v>58195</v>
+        <v>58196</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>137199397</v>
       </c>
       <c r="B280" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>137209378</v>
       </c>
       <c r="B281" t="n">
-        <v>98280</v>
+        <v>98286</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>137199338</v>
       </c>
       <c r="B284" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137199381</v>
       </c>
       <c r="B285" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>137203492</v>
       </c>
       <c r="B286" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>137209361</v>
       </c>
       <c r="B287" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>137209365</v>
       </c>
       <c r="B288" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>137209390</v>
       </c>
       <c r="B289" t="n">
-        <v>98274</v>
+        <v>98280</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>137199414</v>
       </c>
       <c r="B315" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>137209363</v>
       </c>
       <c r="B316" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>137209374</v>
       </c>
       <c r="B317" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>137209379</v>
       </c>
       <c r="B318" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>137209386</v>
       </c>
       <c r="B319" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>137209407</v>
       </c>
       <c r="B320" t="n">
-        <v>79274</v>
+        <v>79279</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>137199418</v>
       </c>
       <c r="B325" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>137209385</v>
       </c>
       <c r="B326" t="n">
-        <v>80106</v>
+        <v>80111</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>137199400</v>
       </c>
       <c r="B327" t="n">
-        <v>79539</v>
+        <v>79544</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199346</v>
       </c>
       <c r="B2" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>137199349</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137209347</v>
       </c>
       <c r="B4" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137209391</v>
       </c>
       <c r="B5" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>137237701</v>
       </c>
       <c r="B6" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137237728</v>
       </c>
       <c r="B7" t="n">
-        <v>79187</v>
+        <v>79198</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137199339</v>
       </c>
       <c r="B8" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137199388</v>
       </c>
       <c r="B9" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137199417</v>
       </c>
       <c r="B10" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137203503</v>
       </c>
       <c r="B11" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>137237700</v>
       </c>
       <c r="B12" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>137237702</v>
       </c>
       <c r="B13" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>137237725</v>
       </c>
       <c r="B14" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137238609</v>
       </c>
       <c r="B15" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137238619</v>
       </c>
       <c r="B16" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137238623</v>
       </c>
       <c r="B17" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>137238624</v>
       </c>
       <c r="B18" t="n">
-        <v>93469</v>
+        <v>93481</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137199403</v>
       </c>
       <c r="B19" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137199406</v>
       </c>
       <c r="B20" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137199408</v>
       </c>
       <c r="B21" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137237704</v>
       </c>
       <c r="B22" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>137237705</v>
       </c>
       <c r="B23" t="n">
-        <v>92190</v>
+        <v>92202</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137199347</v>
       </c>
       <c r="B24" t="n">
-        <v>93495</v>
+        <v>93507</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>137199336</v>
       </c>
       <c r="B96" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>137199341</v>
       </c>
       <c r="B97" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>137199342</v>
       </c>
       <c r="B98" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>137199343</v>
       </c>
       <c r="B99" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>137199351</v>
       </c>
       <c r="B100" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>137199354</v>
       </c>
       <c r="B101" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>137199359</v>
       </c>
       <c r="B102" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>137199360</v>
       </c>
       <c r="B103" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>137199364</v>
       </c>
       <c r="B104" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>137199365</v>
       </c>
       <c r="B105" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>137199378</v>
       </c>
       <c r="B106" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>137199382</v>
       </c>
       <c r="B107" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>137199386</v>
       </c>
       <c r="B108" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>137199387</v>
       </c>
       <c r="B109" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>137199389</v>
       </c>
       <c r="B110" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>137199390</v>
       </c>
       <c r="B111" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>137199395</v>
       </c>
       <c r="B112" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>137199401</v>
       </c>
       <c r="B113" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>137199407</v>
       </c>
       <c r="B114" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>137199416</v>
       </c>
       <c r="B115" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>137199420</v>
       </c>
       <c r="B116" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>137203487</v>
       </c>
       <c r="B117" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>137203488</v>
       </c>
       <c r="B118" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>137203490</v>
       </c>
       <c r="B119" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>137203491</v>
       </c>
       <c r="B120" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>137203493</v>
       </c>
       <c r="B121" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>137203494</v>
       </c>
       <c r="B122" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>137203496</v>
       </c>
       <c r="B123" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>137203502</v>
       </c>
       <c r="B124" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>137203504</v>
       </c>
       <c r="B125" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>137203505</v>
       </c>
       <c r="B126" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>137203506</v>
       </c>
       <c r="B127" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>137203507</v>
       </c>
       <c r="B128" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>137203508</v>
       </c>
       <c r="B129" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>137203509</v>
       </c>
       <c r="B130" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>137203510</v>
       </c>
       <c r="B131" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>137203511</v>
       </c>
       <c r="B132" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>137203512</v>
       </c>
       <c r="B133" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>137203513</v>
       </c>
       <c r="B134" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>137203514</v>
       </c>
       <c r="B135" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>137203515</v>
       </c>
       <c r="B136" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>137209346</v>
       </c>
       <c r="B137" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>137209348</v>
       </c>
       <c r="B138" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>137209349</v>
       </c>
       <c r="B139" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>137209350</v>
       </c>
       <c r="B140" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>137209351</v>
       </c>
       <c r="B141" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>137209353</v>
       </c>
       <c r="B142" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>137209354</v>
       </c>
       <c r="B143" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>137209373</v>
       </c>
       <c r="B144" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>137209384</v>
       </c>
       <c r="B145" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>137209400</v>
       </c>
       <c r="B146" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>137209405</v>
       </c>
       <c r="B147" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>137237706</v>
       </c>
       <c r="B148" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>137237707</v>
       </c>
       <c r="B149" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>137237709</v>
       </c>
       <c r="B150" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>137237712</v>
       </c>
       <c r="B151" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137237713</v>
       </c>
       <c r="B152" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137237714</v>
       </c>
       <c r="B153" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137237715</v>
       </c>
       <c r="B154" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137237719</v>
       </c>
       <c r="B155" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>137237720</v>
       </c>
       <c r="B156" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>137237723</v>
       </c>
       <c r="B157" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137238613</v>
       </c>
       <c r="B158" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>137238614</v>
       </c>
       <c r="B159" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>137238616</v>
       </c>
       <c r="B160" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137238617</v>
       </c>
       <c r="B161" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>137238620</v>
       </c>
       <c r="B162" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>137238621</v>
       </c>
       <c r="B163" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>137238622</v>
       </c>
       <c r="B164" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>137238626</v>
       </c>
       <c r="B165" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>137238627</v>
       </c>
       <c r="B166" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>137238628</v>
       </c>
       <c r="B167" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>137238629</v>
       </c>
       <c r="B168" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>137238631</v>
       </c>
       <c r="B169" t="n">
-        <v>79521</v>
+        <v>79532</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>137199379</v>
       </c>
       <c r="B170" t="n">
-        <v>78924</v>
+        <v>78935</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>137199357</v>
       </c>
       <c r="B186" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>137199419</v>
       </c>
       <c r="B187" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>137237711</v>
       </c>
       <c r="B188" t="n">
-        <v>79278</v>
+        <v>79289</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>137199372</v>
       </c>
       <c r="B204" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>137199380</v>
       </c>
       <c r="B205" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>137199383</v>
       </c>
       <c r="B206" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>137199385</v>
       </c>
       <c r="B207" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>137199394</v>
       </c>
       <c r="B208" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>137199415</v>
       </c>
       <c r="B209" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>137209336</v>
       </c>
       <c r="B210" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>137209342</v>
       </c>
       <c r="B211" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>137209357</v>
       </c>
       <c r="B212" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>137209381</v>
       </c>
       <c r="B213" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>137209383</v>
       </c>
       <c r="B214" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>137209388</v>
       </c>
       <c r="B215" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>137209389</v>
       </c>
       <c r="B216" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>137209392</v>
       </c>
       <c r="B217" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>137209395</v>
       </c>
       <c r="B218" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>137209401</v>
       </c>
       <c r="B219" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>137209408</v>
       </c>
       <c r="B220" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>137209409</v>
       </c>
       <c r="B221" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>137237726</v>
       </c>
       <c r="B222" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>137238630</v>
       </c>
       <c r="B223" t="n">
-        <v>80140</v>
+        <v>80151</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>137199397</v>
       </c>
       <c r="B280" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>137209378</v>
       </c>
       <c r="B281" t="n">
-        <v>98286</v>
+        <v>98298</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>137199338</v>
       </c>
       <c r="B284" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137199381</v>
       </c>
       <c r="B285" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>137203492</v>
       </c>
       <c r="B286" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>137209361</v>
       </c>
       <c r="B287" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>137209365</v>
       </c>
       <c r="B288" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>137209390</v>
       </c>
       <c r="B289" t="n">
-        <v>98280</v>
+        <v>98292</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>137199414</v>
       </c>
       <c r="B315" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>137209363</v>
       </c>
       <c r="B316" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>137209374</v>
       </c>
       <c r="B317" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>137209379</v>
       </c>
       <c r="B318" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>137209386</v>
       </c>
       <c r="B319" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>137209407</v>
       </c>
       <c r="B320" t="n">
-        <v>79279</v>
+        <v>79290</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>137199418</v>
       </c>
       <c r="B325" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>137209385</v>
       </c>
       <c r="B326" t="n">
-        <v>80111</v>
+        <v>80122</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>137199400</v>
       </c>
       <c r="B327" t="n">
-        <v>79544</v>
+        <v>79555</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199346</v>
       </c>
       <c r="B2" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>137199349</v>
       </c>
       <c r="B3" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137209347</v>
       </c>
       <c r="B4" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137209391</v>
       </c>
       <c r="B5" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>137237701</v>
       </c>
       <c r="B6" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137237728</v>
       </c>
       <c r="B7" t="n">
-        <v>79198</v>
+        <v>79199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137199339</v>
       </c>
       <c r="B8" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137199388</v>
       </c>
       <c r="B9" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137199417</v>
       </c>
       <c r="B10" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137203503</v>
       </c>
       <c r="B11" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>137237700</v>
       </c>
       <c r="B12" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>137237702</v>
       </c>
       <c r="B13" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>137237725</v>
       </c>
       <c r="B14" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137238609</v>
       </c>
       <c r="B15" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137238619</v>
       </c>
       <c r="B16" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137238623</v>
       </c>
       <c r="B17" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>137238624</v>
       </c>
       <c r="B18" t="n">
-        <v>93481</v>
+        <v>93482</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137199403</v>
       </c>
       <c r="B19" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137199406</v>
       </c>
       <c r="B20" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137199408</v>
       </c>
       <c r="B21" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137237704</v>
       </c>
       <c r="B22" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>137237705</v>
       </c>
       <c r="B23" t="n">
-        <v>92202</v>
+        <v>92203</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137199347</v>
       </c>
       <c r="B24" t="n">
-        <v>93507</v>
+        <v>93508</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>137199336</v>
       </c>
       <c r="B96" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>137199341</v>
       </c>
       <c r="B97" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>137199342</v>
       </c>
       <c r="B98" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>137199343</v>
       </c>
       <c r="B99" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>137199351</v>
       </c>
       <c r="B100" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>137199354</v>
       </c>
       <c r="B101" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>137199359</v>
       </c>
       <c r="B102" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>137199360</v>
       </c>
       <c r="B103" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>137199364</v>
       </c>
       <c r="B104" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>137199365</v>
       </c>
       <c r="B105" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>137199378</v>
       </c>
       <c r="B106" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>137199382</v>
       </c>
       <c r="B107" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>137199386</v>
       </c>
       <c r="B108" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>137199387</v>
       </c>
       <c r="B109" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>137199389</v>
       </c>
       <c r="B110" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>137199390</v>
       </c>
       <c r="B111" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>137199395</v>
       </c>
       <c r="B112" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>137199401</v>
       </c>
       <c r="B113" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>137199407</v>
       </c>
       <c r="B114" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>137199416</v>
       </c>
       <c r="B115" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>137199420</v>
       </c>
       <c r="B116" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>137203487</v>
       </c>
       <c r="B117" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>137203488</v>
       </c>
       <c r="B118" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>137203490</v>
       </c>
       <c r="B119" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>137203491</v>
       </c>
       <c r="B120" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>137203493</v>
       </c>
       <c r="B121" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>137203494</v>
       </c>
       <c r="B122" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>137203496</v>
       </c>
       <c r="B123" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>137203502</v>
       </c>
       <c r="B124" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>137203504</v>
       </c>
       <c r="B125" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>137203505</v>
       </c>
       <c r="B126" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>137203506</v>
       </c>
       <c r="B127" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>137203507</v>
       </c>
       <c r="B128" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>137203508</v>
       </c>
       <c r="B129" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>137203509</v>
       </c>
       <c r="B130" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>137203510</v>
       </c>
       <c r="B131" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>137203511</v>
       </c>
       <c r="B132" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>137203512</v>
       </c>
       <c r="B133" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>137203513</v>
       </c>
       <c r="B134" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>137203514</v>
       </c>
       <c r="B135" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>137203515</v>
       </c>
       <c r="B136" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>137209346</v>
       </c>
       <c r="B137" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>137209348</v>
       </c>
       <c r="B138" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>137209349</v>
       </c>
       <c r="B139" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>137209350</v>
       </c>
       <c r="B140" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>137209351</v>
       </c>
       <c r="B141" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>137209353</v>
       </c>
       <c r="B142" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>137209354</v>
       </c>
       <c r="B143" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>137209373</v>
       </c>
       <c r="B144" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>137209384</v>
       </c>
       <c r="B145" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>137209400</v>
       </c>
       <c r="B146" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>137209405</v>
       </c>
       <c r="B147" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>137237706</v>
       </c>
       <c r="B148" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>137237707</v>
       </c>
       <c r="B149" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>137237709</v>
       </c>
       <c r="B150" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>137237712</v>
       </c>
       <c r="B151" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137237713</v>
       </c>
       <c r="B152" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137237714</v>
       </c>
       <c r="B153" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137237715</v>
       </c>
       <c r="B154" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137237719</v>
       </c>
       <c r="B155" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>137237720</v>
       </c>
       <c r="B156" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>137237723</v>
       </c>
       <c r="B157" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137238613</v>
       </c>
       <c r="B158" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>137238614</v>
       </c>
       <c r="B159" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>137238616</v>
       </c>
       <c r="B160" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137238617</v>
       </c>
       <c r="B161" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>137238620</v>
       </c>
       <c r="B162" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>137238621</v>
       </c>
       <c r="B163" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>137238622</v>
       </c>
       <c r="B164" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>137238626</v>
       </c>
       <c r="B165" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>137238627</v>
       </c>
       <c r="B166" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>137238628</v>
       </c>
       <c r="B167" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>137238629</v>
       </c>
       <c r="B168" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>137238631</v>
       </c>
       <c r="B169" t="n">
-        <v>79532</v>
+        <v>79533</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>137199379</v>
       </c>
       <c r="B170" t="n">
-        <v>78935</v>
+        <v>78936</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>137199357</v>
       </c>
       <c r="B186" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>137199419</v>
       </c>
       <c r="B187" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>137237711</v>
       </c>
       <c r="B188" t="n">
-        <v>79289</v>
+        <v>79290</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>137199372</v>
       </c>
       <c r="B204" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>137199380</v>
       </c>
       <c r="B205" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>137199383</v>
       </c>
       <c r="B206" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>137199385</v>
       </c>
       <c r="B207" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>137199394</v>
       </c>
       <c r="B208" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>137199415</v>
       </c>
       <c r="B209" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>137209336</v>
       </c>
       <c r="B210" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>137209342</v>
       </c>
       <c r="B211" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>137209357</v>
       </c>
       <c r="B212" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>137209381</v>
       </c>
       <c r="B213" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>137209383</v>
       </c>
       <c r="B214" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>137209388</v>
       </c>
       <c r="B215" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>137209389</v>
       </c>
       <c r="B216" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>137209392</v>
       </c>
       <c r="B217" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>137209395</v>
       </c>
       <c r="B218" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>137209401</v>
       </c>
       <c r="B219" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>137209408</v>
       </c>
       <c r="B220" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>137209409</v>
       </c>
       <c r="B221" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>137237726</v>
       </c>
       <c r="B222" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>137238630</v>
       </c>
       <c r="B223" t="n">
-        <v>80151</v>
+        <v>80152</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>137199397</v>
       </c>
       <c r="B280" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>137209378</v>
       </c>
       <c r="B281" t="n">
-        <v>98298</v>
+        <v>98299</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>137199338</v>
       </c>
       <c r="B284" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137199381</v>
       </c>
       <c r="B285" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>137203492</v>
       </c>
       <c r="B286" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>137209361</v>
       </c>
       <c r="B287" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>137209365</v>
       </c>
       <c r="B288" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>137209390</v>
       </c>
       <c r="B289" t="n">
-        <v>98292</v>
+        <v>98293</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>137199414</v>
       </c>
       <c r="B315" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>137209363</v>
       </c>
       <c r="B316" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>137209374</v>
       </c>
       <c r="B317" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>137209379</v>
       </c>
       <c r="B318" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>137209386</v>
       </c>
       <c r="B319" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>137209407</v>
       </c>
       <c r="B320" t="n">
-        <v>79290</v>
+        <v>79291</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>137199418</v>
       </c>
       <c r="B325" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>137209385</v>
       </c>
       <c r="B326" t="n">
-        <v>80122</v>
+        <v>80123</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>137199400</v>
       </c>
       <c r="B327" t="n">
-        <v>79555</v>
+        <v>79556</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199346</v>
       </c>
       <c r="B2" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>137199349</v>
       </c>
       <c r="B3" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137209347</v>
       </c>
       <c r="B4" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137209391</v>
       </c>
       <c r="B5" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>137237701</v>
       </c>
       <c r="B6" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137237728</v>
       </c>
       <c r="B7" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137199339</v>
       </c>
       <c r="B8" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137199388</v>
       </c>
       <c r="B9" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137199417</v>
       </c>
       <c r="B10" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137203503</v>
       </c>
       <c r="B11" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>137237700</v>
       </c>
       <c r="B12" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>137237702</v>
       </c>
       <c r="B13" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>137237725</v>
       </c>
       <c r="B14" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137238609</v>
       </c>
       <c r="B15" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137238619</v>
       </c>
       <c r="B16" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137238623</v>
       </c>
       <c r="B17" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>137238624</v>
       </c>
       <c r="B18" t="n">
-        <v>93482</v>
+        <v>93485</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137199403</v>
       </c>
       <c r="B19" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137199406</v>
       </c>
       <c r="B20" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137199408</v>
       </c>
       <c r="B21" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137237704</v>
       </c>
       <c r="B22" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>137237705</v>
       </c>
       <c r="B23" t="n">
-        <v>92203</v>
+        <v>92206</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137199347</v>
       </c>
       <c r="B24" t="n">
-        <v>93508</v>
+        <v>93511</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>137199336</v>
       </c>
       <c r="B96" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>137199341</v>
       </c>
       <c r="B97" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>137199342</v>
       </c>
       <c r="B98" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>137199343</v>
       </c>
       <c r="B99" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>137199351</v>
       </c>
       <c r="B100" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>137199354</v>
       </c>
       <c r="B101" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>137199359</v>
       </c>
       <c r="B102" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>137199360</v>
       </c>
       <c r="B103" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>137199364</v>
       </c>
       <c r="B104" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>137199365</v>
       </c>
       <c r="B105" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>137199378</v>
       </c>
       <c r="B106" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>137199382</v>
       </c>
       <c r="B107" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>137199386</v>
       </c>
       <c r="B108" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>137199387</v>
       </c>
       <c r="B109" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>137199389</v>
       </c>
       <c r="B110" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>137199390</v>
       </c>
       <c r="B111" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>137199395</v>
       </c>
       <c r="B112" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>137199401</v>
       </c>
       <c r="B113" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>137199407</v>
       </c>
       <c r="B114" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>137199416</v>
       </c>
       <c r="B115" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>137199420</v>
       </c>
       <c r="B116" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>137203487</v>
       </c>
       <c r="B117" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>137203488</v>
       </c>
       <c r="B118" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>137203490</v>
       </c>
       <c r="B119" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>137203491</v>
       </c>
       <c r="B120" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>137203493</v>
       </c>
       <c r="B121" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>137203494</v>
       </c>
       <c r="B122" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>137203496</v>
       </c>
       <c r="B123" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>137203502</v>
       </c>
       <c r="B124" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>137203504</v>
       </c>
       <c r="B125" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>137203505</v>
       </c>
       <c r="B126" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>137203506</v>
       </c>
       <c r="B127" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>137203507</v>
       </c>
       <c r="B128" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>137203508</v>
       </c>
       <c r="B129" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>137203509</v>
       </c>
       <c r="B130" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>137203510</v>
       </c>
       <c r="B131" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>137203511</v>
       </c>
       <c r="B132" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>137203512</v>
       </c>
       <c r="B133" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>137203513</v>
       </c>
       <c r="B134" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>137203514</v>
       </c>
       <c r="B135" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>137203515</v>
       </c>
       <c r="B136" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>137209346</v>
       </c>
       <c r="B137" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>137209348</v>
       </c>
       <c r="B138" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>137209349</v>
       </c>
       <c r="B139" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>137209350</v>
       </c>
       <c r="B140" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>137209351</v>
       </c>
       <c r="B141" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>137209353</v>
       </c>
       <c r="B142" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>137209354</v>
       </c>
       <c r="B143" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>137209373</v>
       </c>
       <c r="B144" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>137209384</v>
       </c>
       <c r="B145" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>137209400</v>
       </c>
       <c r="B146" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>137209405</v>
       </c>
       <c r="B147" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>137237706</v>
       </c>
       <c r="B148" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>137237707</v>
       </c>
       <c r="B149" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>137237709</v>
       </c>
       <c r="B150" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>137237712</v>
       </c>
       <c r="B151" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137237713</v>
       </c>
       <c r="B152" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137237714</v>
       </c>
       <c r="B153" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137237715</v>
       </c>
       <c r="B154" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137237719</v>
       </c>
       <c r="B155" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>137237720</v>
       </c>
       <c r="B156" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>137237723</v>
       </c>
       <c r="B157" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137238613</v>
       </c>
       <c r="B158" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>137238614</v>
       </c>
       <c r="B159" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>137238616</v>
       </c>
       <c r="B160" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137238617</v>
       </c>
       <c r="B161" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>137238620</v>
       </c>
       <c r="B162" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>137238621</v>
       </c>
       <c r="B163" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>137238622</v>
       </c>
       <c r="B164" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>137238626</v>
       </c>
       <c r="B165" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>137238627</v>
       </c>
       <c r="B166" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>137238628</v>
       </c>
       <c r="B167" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>137238629</v>
       </c>
       <c r="B168" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>137238631</v>
       </c>
       <c r="B169" t="n">
-        <v>79533</v>
+        <v>79535</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>137199379</v>
       </c>
       <c r="B170" t="n">
-        <v>78936</v>
+        <v>78938</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>137199357</v>
       </c>
       <c r="B186" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>137199419</v>
       </c>
       <c r="B187" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>137237711</v>
       </c>
       <c r="B188" t="n">
-        <v>79290</v>
+        <v>79292</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>137199372</v>
       </c>
       <c r="B204" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>137199380</v>
       </c>
       <c r="B205" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>137199383</v>
       </c>
       <c r="B206" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>137199385</v>
       </c>
       <c r="B207" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>137199394</v>
       </c>
       <c r="B208" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>137199415</v>
       </c>
       <c r="B209" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>137209336</v>
       </c>
       <c r="B210" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>137209342</v>
       </c>
       <c r="B211" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>137209357</v>
       </c>
       <c r="B212" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>137209381</v>
       </c>
       <c r="B213" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>137209383</v>
       </c>
       <c r="B214" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>137209388</v>
       </c>
       <c r="B215" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>137209389</v>
       </c>
       <c r="B216" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>137209392</v>
       </c>
       <c r="B217" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>137209395</v>
       </c>
       <c r="B218" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>137209401</v>
       </c>
       <c r="B219" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>137209408</v>
       </c>
       <c r="B220" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>137209409</v>
       </c>
       <c r="B221" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>137237726</v>
       </c>
       <c r="B222" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>137238630</v>
       </c>
       <c r="B223" t="n">
-        <v>80152</v>
+        <v>80154</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>137199397</v>
       </c>
       <c r="B280" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>137209378</v>
       </c>
       <c r="B281" t="n">
-        <v>98299</v>
+        <v>98302</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>137199338</v>
       </c>
       <c r="B284" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137199381</v>
       </c>
       <c r="B285" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>137203492</v>
       </c>
       <c r="B286" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>137209361</v>
       </c>
       <c r="B287" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>137209365</v>
       </c>
       <c r="B288" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>137209390</v>
       </c>
       <c r="B289" t="n">
-        <v>98293</v>
+        <v>98296</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>137199414</v>
       </c>
       <c r="B315" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>137209363</v>
       </c>
       <c r="B316" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>137209374</v>
       </c>
       <c r="B317" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>137209379</v>
       </c>
       <c r="B318" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>137209386</v>
       </c>
       <c r="B319" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>137209407</v>
       </c>
       <c r="B320" t="n">
-        <v>79291</v>
+        <v>79293</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>137199418</v>
       </c>
       <c r="B325" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>137209385</v>
       </c>
       <c r="B326" t="n">
-        <v>80123</v>
+        <v>80125</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>137199400</v>
       </c>
       <c r="B327" t="n">
-        <v>79556</v>
+        <v>79558</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>

--- a/artfynd/A 34895-2026 artfynd.xlsx
+++ b/artfynd/A 34895-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>137199346</v>
       </c>
       <c r="B2" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -805,7 +805,7 @@
         <v>137199349</v>
       </c>
       <c r="B3" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -927,7 +927,7 @@
         <v>137209347</v>
       </c>
       <c r="B4" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>137209391</v>
       </c>
       <c r="B5" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1156,7 +1156,7 @@
         <v>137237701</v>
       </c>
       <c r="B6" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>137237728</v>
       </c>
       <c r="B7" t="n">
-        <v>79201</v>
+        <v>79205</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1380,7 +1380,7 @@
         <v>137199339</v>
       </c>
       <c r="B8" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1506,7 +1506,7 @@
         <v>137199388</v>
       </c>
       <c r="B9" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1632,7 +1632,7 @@
         <v>137199417</v>
       </c>
       <c r="B10" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1753,7 +1753,7 @@
         <v>137203503</v>
       </c>
       <c r="B11" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1865,7 +1865,7 @@
         <v>137237700</v>
       </c>
       <c r="B12" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1986,7 +1986,7 @@
         <v>137237702</v>
       </c>
       <c r="B13" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>137237725</v>
       </c>
       <c r="B14" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2228,7 +2228,7 @@
         <v>137238609</v>
       </c>
       <c r="B15" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2352,7 +2352,7 @@
         <v>137238619</v>
       </c>
       <c r="B16" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2476,7 +2476,7 @@
         <v>137238623</v>
       </c>
       <c r="B17" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2600,7 +2600,7 @@
         <v>137238624</v>
       </c>
       <c r="B18" t="n">
-        <v>93485</v>
+        <v>93489</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2724,7 +2724,7 @@
         <v>137199403</v>
       </c>
       <c r="B19" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2845,7 +2845,7 @@
         <v>137199406</v>
       </c>
       <c r="B20" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2969,7 +2969,7 @@
         <v>137199408</v>
       </c>
       <c r="B21" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         <v>137237704</v>
       </c>
       <c r="B22" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3211,7 +3211,7 @@
         <v>137237705</v>
       </c>
       <c r="B23" t="n">
-        <v>92206</v>
+        <v>92210</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3327,7 +3327,7 @@
         <v>137199347</v>
       </c>
       <c r="B24" t="n">
-        <v>93511</v>
+        <v>93515</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -11281,7 +11281,7 @@
         <v>137199336</v>
       </c>
       <c r="B96" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11393,7 +11393,7 @@
         <v>137199341</v>
       </c>
       <c r="B97" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11505,7 +11505,7 @@
         <v>137199342</v>
       </c>
       <c r="B98" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11617,7 +11617,7 @@
         <v>137199343</v>
       </c>
       <c r="B99" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -11729,7 +11729,7 @@
         <v>137199351</v>
       </c>
       <c r="B100" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11841,7 +11841,7 @@
         <v>137199354</v>
       </c>
       <c r="B101" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11953,7 +11953,7 @@
         <v>137199359</v>
       </c>
       <c r="B102" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -12065,7 +12065,7 @@
         <v>137199360</v>
       </c>
       <c r="B103" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -12177,7 +12177,7 @@
         <v>137199364</v>
       </c>
       <c r="B104" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -12289,7 +12289,7 @@
         <v>137199365</v>
       </c>
       <c r="B105" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -12401,7 +12401,7 @@
         <v>137199378</v>
       </c>
       <c r="B106" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -12513,7 +12513,7 @@
         <v>137199382</v>
       </c>
       <c r="B107" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12625,7 +12625,7 @@
         <v>137199386</v>
       </c>
       <c r="B108" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -12737,7 +12737,7 @@
         <v>137199387</v>
       </c>
       <c r="B109" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -12849,7 +12849,7 @@
         <v>137199389</v>
       </c>
       <c r="B110" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12961,7 +12961,7 @@
         <v>137199390</v>
       </c>
       <c r="B111" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -13073,7 +13073,7 @@
         <v>137199395</v>
       </c>
       <c r="B112" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -13185,7 +13185,7 @@
         <v>137199401</v>
       </c>
       <c r="B113" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -13297,7 +13297,7 @@
         <v>137199407</v>
       </c>
       <c r="B114" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13413,7 +13413,7 @@
         <v>137199416</v>
       </c>
       <c r="B115" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -13525,7 +13525,7 @@
         <v>137199420</v>
       </c>
       <c r="B116" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -13637,7 +13637,7 @@
         <v>137203487</v>
       </c>
       <c r="B117" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13749,7 +13749,7 @@
         <v>137203488</v>
       </c>
       <c r="B118" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -13861,7 +13861,7 @@
         <v>137203490</v>
       </c>
       <c r="B119" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13973,7 +13973,7 @@
         <v>137203491</v>
       </c>
       <c r="B120" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -14085,7 +14085,7 @@
         <v>137203493</v>
       </c>
       <c r="B121" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -14197,7 +14197,7 @@
         <v>137203494</v>
       </c>
       <c r="B122" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -14309,7 +14309,7 @@
         <v>137203496</v>
       </c>
       <c r="B123" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
         <v>137203502</v>
       </c>
       <c r="B124" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14533,7 +14533,7 @@
         <v>137203504</v>
       </c>
       <c r="B125" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14645,7 +14645,7 @@
         <v>137203505</v>
       </c>
       <c r="B126" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14757,7 +14757,7 @@
         <v>137203506</v>
       </c>
       <c r="B127" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -14869,7 +14869,7 @@
         <v>137203507</v>
       </c>
       <c r="B128" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -14981,7 +14981,7 @@
         <v>137203508</v>
       </c>
       <c r="B129" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -15093,7 +15093,7 @@
         <v>137203509</v>
       </c>
       <c r="B130" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -15205,7 +15205,7 @@
         <v>137203510</v>
       </c>
       <c r="B131" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -15317,7 +15317,7 @@
         <v>137203511</v>
       </c>
       <c r="B132" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15429,7 +15429,7 @@
         <v>137203512</v>
       </c>
       <c r="B133" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15541,7 +15541,7 @@
         <v>137203513</v>
       </c>
       <c r="B134" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15653,7 +15653,7 @@
         <v>137203514</v>
       </c>
       <c r="B135" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15765,7 +15765,7 @@
         <v>137203515</v>
       </c>
       <c r="B136" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15877,7 +15877,7 @@
         <v>137209346</v>
       </c>
       <c r="B137" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15989,7 +15989,7 @@
         <v>137209348</v>
       </c>
       <c r="B138" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -16101,7 +16101,7 @@
         <v>137209349</v>
       </c>
       <c r="B139" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16213,7 +16213,7 @@
         <v>137209350</v>
       </c>
       <c r="B140" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16325,7 +16325,7 @@
         <v>137209351</v>
       </c>
       <c r="B141" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16437,7 +16437,7 @@
         <v>137209353</v>
       </c>
       <c r="B142" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -16549,7 +16549,7 @@
         <v>137209354</v>
       </c>
       <c r="B143" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16661,7 +16661,7 @@
         <v>137209373</v>
       </c>
       <c r="B144" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16773,7 +16773,7 @@
         <v>137209384</v>
       </c>
       <c r="B145" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16885,7 +16885,7 @@
         <v>137209400</v>
       </c>
       <c r="B146" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16997,7 +16997,7 @@
         <v>137209405</v>
       </c>
       <c r="B147" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -17109,7 +17109,7 @@
         <v>137237706</v>
       </c>
       <c r="B148" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -17221,7 +17221,7 @@
         <v>137237707</v>
       </c>
       <c r="B149" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -17333,7 +17333,7 @@
         <v>137237709</v>
       </c>
       <c r="B150" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17445,7 +17445,7 @@
         <v>137237712</v>
       </c>
       <c r="B151" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17557,7 +17557,7 @@
         <v>137237713</v>
       </c>
       <c r="B152" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17669,7 +17669,7 @@
         <v>137237714</v>
       </c>
       <c r="B153" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17781,7 +17781,7 @@
         <v>137237715</v>
       </c>
       <c r="B154" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17893,7 +17893,7 @@
         <v>137237719</v>
       </c>
       <c r="B155" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -18005,7 +18005,7 @@
         <v>137237720</v>
       </c>
       <c r="B156" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -18117,7 +18117,7 @@
         <v>137237723</v>
       </c>
       <c r="B157" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -18229,7 +18229,7 @@
         <v>137238613</v>
       </c>
       <c r="B158" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>137238614</v>
       </c>
       <c r="B159" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18453,7 +18453,7 @@
         <v>137238616</v>
       </c>
       <c r="B160" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18565,7 +18565,7 @@
         <v>137238617</v>
       </c>
       <c r="B161" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -18677,7 +18677,7 @@
         <v>137238620</v>
       </c>
       <c r="B162" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18789,7 +18789,7 @@
         <v>137238621</v>
       </c>
       <c r="B163" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18901,7 +18901,7 @@
         <v>137238622</v>
       </c>
       <c r="B164" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -19013,7 +19013,7 @@
         <v>137238626</v>
       </c>
       <c r="B165" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -19125,7 +19125,7 @@
         <v>137238627</v>
       </c>
       <c r="B166" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -19237,7 +19237,7 @@
         <v>137238628</v>
       </c>
       <c r="B167" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -19349,7 +19349,7 @@
         <v>137238629</v>
       </c>
       <c r="B168" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19461,7 +19461,7 @@
         <v>137238631</v>
       </c>
       <c r="B169" t="n">
-        <v>79535</v>
+        <v>79539</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -19573,7 +19573,7 @@
         <v>137199379</v>
       </c>
       <c r="B170" t="n">
-        <v>78938</v>
+        <v>78942</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -21285,7 +21285,7 @@
         <v>137199357</v>
       </c>
       <c r="B186" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -21412,7 +21412,7 @@
         <v>137199419</v>
       </c>
       <c r="B187" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -21534,7 +21534,7 @@
         <v>137237711</v>
       </c>
       <c r="B188" t="n">
-        <v>79292</v>
+        <v>79296</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -23312,7 +23312,7 @@
         <v>137199372</v>
       </c>
       <c r="B204" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -23434,7 +23434,7 @@
         <v>137199380</v>
       </c>
       <c r="B205" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -23556,7 +23556,7 @@
         <v>137199383</v>
       </c>
       <c r="B206" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -23678,7 +23678,7 @@
         <v>137199385</v>
       </c>
       <c r="B207" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -23790,7 +23790,7 @@
         <v>137199394</v>
       </c>
       <c r="B208" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -23906,7 +23906,7 @@
         <v>137199415</v>
       </c>
       <c r="B209" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -24028,7 +24028,7 @@
         <v>137209336</v>
       </c>
       <c r="B210" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -24140,7 +24140,7 @@
         <v>137209342</v>
       </c>
       <c r="B211" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -24252,7 +24252,7 @@
         <v>137209357</v>
       </c>
       <c r="B212" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -24364,7 +24364,7 @@
         <v>137209381</v>
       </c>
       <c r="B213" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -24476,7 +24476,7 @@
         <v>137209383</v>
       </c>
       <c r="B214" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -24588,7 +24588,7 @@
         <v>137209388</v>
       </c>
       <c r="B215" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -24700,7 +24700,7 @@
         <v>137209389</v>
       </c>
       <c r="B216" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -24812,7 +24812,7 @@
         <v>137209392</v>
       </c>
       <c r="B217" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -24924,7 +24924,7 @@
         <v>137209395</v>
       </c>
       <c r="B218" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -25036,7 +25036,7 @@
         <v>137209401</v>
       </c>
       <c r="B219" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -25148,7 +25148,7 @@
         <v>137209408</v>
       </c>
       <c r="B220" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -25260,7 +25260,7 @@
         <v>137209409</v>
       </c>
       <c r="B221" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -25372,7 +25372,7 @@
         <v>137237726</v>
       </c>
       <c r="B222" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -25484,7 +25484,7 @@
         <v>137238630</v>
       </c>
       <c r="B223" t="n">
-        <v>80154</v>
+        <v>80158</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -25830,7 +25830,7 @@
         <v>137199358</v>
       </c>
       <c r="B226" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -25943,7 +25943,7 @@
         <v>137199362</v>
       </c>
       <c r="B227" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -26056,7 +26056,7 @@
         <v>137199370</v>
       </c>
       <c r="B228" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -26169,7 +26169,7 @@
         <v>137199371</v>
       </c>
       <c r="B229" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -26282,7 +26282,7 @@
         <v>137199384</v>
       </c>
       <c r="B230" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -26395,7 +26395,7 @@
         <v>137199399</v>
       </c>
       <c r="B231" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -26508,7 +26508,7 @@
         <v>137199367</v>
       </c>
       <c r="B232" t="n">
-        <v>58035</v>
+        <v>58038</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -26738,7 +26738,7 @@
         <v>137199332</v>
       </c>
       <c r="B234" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -26851,7 +26851,7 @@
         <v>137199334</v>
       </c>
       <c r="B235" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -26964,7 +26964,7 @@
         <v>137199337</v>
       </c>
       <c r="B236" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -27078,7 +27078,7 @@
         <v>137199350</v>
       </c>
       <c r="B237" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -27192,7 +27192,7 @@
         <v>137199353</v>
       </c>
       <c r="B238" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -27305,7 +27305,7 @@
         <v>137199355</v>
       </c>
       <c r="B239" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -27418,7 +27418,7 @@
         <v>137199356</v>
       </c>
       <c r="B240" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -27531,7 +27531,7 @@
         <v>137199376</v>
       </c>
       <c r="B241" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -27644,7 +27644,7 @@
         <v>137199392</v>
       </c>
       <c r="B242" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -27757,7 +27757,7 @@
         <v>137199393</v>
       </c>
       <c r="B243" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -27870,7 +27870,7 @@
         <v>137199404</v>
       </c>
       <c r="B244" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -27983,7 +27983,7 @@
         <v>137199410</v>
       </c>
       <c r="B245" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -28096,7 +28096,7 @@
         <v>137199411</v>
       </c>
       <c r="B246" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -28209,7 +28209,7 @@
         <v>137209406</v>
       </c>
       <c r="B247" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -28326,7 +28326,7 @@
         <v>137237721</v>
       </c>
       <c r="B248" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -28443,7 +28443,7 @@
         <v>137237811</v>
       </c>
       <c r="B249" t="n">
-        <v>57221</v>
+        <v>57224</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -28788,7 +28788,7 @@
         <v>137203501</v>
       </c>
       <c r="B252" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -28900,7 +28900,7 @@
         <v>137238615</v>
       </c>
       <c r="B253" t="n">
-        <v>58196</v>
+        <v>58199</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -29359,7 +29359,7 @@
         <v>137199409</v>
       </c>
       <c r="B257" t="n">
-        <v>56598</v>
+        <v>56601</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -32061,7 +32061,7 @@
         <v>137199397</v>
       </c>
       <c r="B280" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -32182,7 +32182,7 @@
         <v>137209378</v>
       </c>
       <c r="B281" t="n">
-        <v>98302</v>
+        <v>98306</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -32513,7 +32513,7 @@
         <v>137199338</v>
       </c>
       <c r="B284" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -32625,7 +32625,7 @@
         <v>137199381</v>
       </c>
       <c r="B285" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -32737,7 +32737,7 @@
         <v>137203492</v>
       </c>
       <c r="B286" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -32849,7 +32849,7 @@
         <v>137209361</v>
       </c>
       <c r="B287" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -32966,7 +32966,7 @@
         <v>137209365</v>
       </c>
       <c r="B288" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -33078,7 +33078,7 @@
         <v>137209390</v>
       </c>
       <c r="B289" t="n">
-        <v>98296</v>
+        <v>98300</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -35891,7 +35891,7 @@
         <v>137199414</v>
       </c>
       <c r="B315" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -36013,7 +36013,7 @@
         <v>137209363</v>
       </c>
       <c r="B316" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -36125,7 +36125,7 @@
         <v>137209374</v>
       </c>
       <c r="B317" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -36237,7 +36237,7 @@
         <v>137209379</v>
       </c>
       <c r="B318" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -36350,7 +36350,7 @@
         <v>137209386</v>
       </c>
       <c r="B319" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -36462,7 +36462,7 @@
         <v>137209407</v>
       </c>
       <c r="B320" t="n">
-        <v>79293</v>
+        <v>79297</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -37013,7 +37013,7 @@
         <v>137199418</v>
       </c>
       <c r="B325" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -37135,7 +37135,7 @@
         <v>137209385</v>
       </c>
       <c r="B326" t="n">
-        <v>80125</v>
+        <v>80129</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -37247,7 +37247,7 @@
         <v>137199400</v>
       </c>
       <c r="B327" t="n">
-        <v>79558</v>
+        <v>79562</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
